--- a/input_data/kinetic_params.xlsx
+++ b/input_data/kinetic_params.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Central" sheetId="1" state="visible" r:id="rId2"/>
@@ -18,6 +18,7 @@
     <sheet name="Gene Expression" sheetId="8" state="visible" r:id="rId9"/>
     <sheet name="SSU Assembly" sheetId="9" state="visible" r:id="rId10"/>
     <sheet name="LSU Assembly" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="LSU Assembly w. 4 L7s" sheetId="11" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6717" uniqueCount="1091">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6823" uniqueCount="1094">
   <si>
     <t xml:space="preserve">Reaction Name</t>
   </si>
@@ -2973,7 +2974,7 @@
     <t xml:space="preserve">product</t>
   </si>
   <si>
-    <t xml:space="preserve">rate /microM/Sec </t>
+    <t xml:space="preserve">rate /microM/Sec</t>
   </si>
   <si>
     <t xml:space="preserve">s4</t>
@@ -3322,6 +3323,15 @@
   </si>
   <si>
     <t xml:space="preserve">R5SL1L2L3L4L5L6L7L9L10L11L13L14L15L16L17L18L19L20L21L22L23L24L27L28L29L31L32L33L34L35L36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L7L7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R5SL1L2L3L4L5L6L7L7L9L10L11L13L14L15L16L17L18L19L20L21L22L23L24L27L28L29L31L32L33L34L35L36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R5SL1L2L3L4L5L6L7L7L7L7L9L10L11L13L14L15L16L17L18L19L20L21L22L23L24L27L28L29L31L32L33L34L35L36</t>
   </si>
 </sst>
 </file>
@@ -3576,7 +3586,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F161"/>
-  <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.4453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.66"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.33"/>
@@ -6598,7 +6608,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7578125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="26" width="15.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="26" width="91.69"/>
@@ -7066,6 +7076,521 @@
       </c>
       <c r="D33" s="26" t="n">
         <v>0.01</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D35"/>
+  <sheetFormatPr defaultColWidth="8.78515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="26" width="15.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="26" width="91.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="26" width="90.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.09"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="25" t="s">
+        <v>971</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>972</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>973</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="26" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>976</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>1028</v>
+      </c>
+      <c r="D2" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="26" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D3" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="26" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>1032</v>
+      </c>
+      <c r="D4" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="26" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>1034</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="26" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="26" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>1038</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="26" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="26" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="26" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="26" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="26" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C12" s="26" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="26" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="26" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="26" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="26" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="26" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="26" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="26" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="26" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="26" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="26" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="26" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="26" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C24" s="26" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="26" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="26" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="26" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="26" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="26" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="26" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="26" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C31" s="26" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D31" s="26" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="26" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C32" s="26" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D32" s="26" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="26" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C33" s="26" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D33" s="26" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="26" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C34" s="26" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D34" s="26" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="26" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C35" s="26" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7085,7 +7610,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F329"/>
-  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.94140625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.83"/>
@@ -13236,7 +13761,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F113"/>
-  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.94140625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.66"/>
@@ -15358,7 +15883,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F104"/>
-  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.94140625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19"/>
@@ -17339,7 +17864,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F436"/>
-  <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.94140625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.5"/>
@@ -25378,7 +25903,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D87"/>
-  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
@@ -26361,7 +26886,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D121"/>
-  <sheetFormatPr defaultColWidth="11.95703125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.9921875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.35"/>
   </cols>
@@ -27957,12 +28482,12 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.76953125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="28.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="24.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="6" width="40.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="17.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="6" width="17.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="8" width="15.62"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="6" style="9" width="8.73"/>
   </cols>
@@ -28421,7 +28946,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.62"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="43.83"/>
